--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4989-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4989-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F458DF4-7E0A-415A-9BA2-0248317EF3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EE95AFF-CFFE-4750-9659-AA30D3315946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5B1CA484-88E1-490C-858A-1995276644CD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6E7C75D4-FF95-4EED-9389-2CE17373F5FD}"/>
   </bookViews>
   <sheets>
     <sheet name="4989-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1466,30 +1466,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B98141B0-1B42-4E4C-AF00-121C89424AD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AAD92B-650D-4646-B0CD-DC1EB09F3D16}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1679,7 +1679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2023</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>29</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>29</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2021</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>29</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2020</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2019</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2018</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2017</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2016</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2014</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2013</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2012</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2011</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2010</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>43</v>
       </c>
